--- a/01_Thermal/B_results/single_annular_gp_analysis.xlsx
+++ b/01_Thermal/B_results/single_annular_gp_analysis.xlsx
@@ -483,16 +483,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>16.20849910779122</v>
+        <v>0.5561264840321801</v>
       </c>
       <c r="E2" t="n">
-        <v>2.588981247422754</v>
+        <v>0.0105389893474099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1296264569840294</v>
+        <v>0.004869212653042428</v>
       </c>
       <c r="G2" t="n">
-        <v>201.6975596807746</v>
+        <v>0.2845973329614411</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -511,16 +511,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>6.694335390760429</v>
+        <v>0.6127779690978017</v>
       </c>
       <c r="E3" t="n">
-        <v>1.113481064610395</v>
+        <v>0.04757893444987597</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06149910418711423</v>
+        <v>0.006235304398978792</v>
       </c>
       <c r="G3" t="n">
-        <v>37.07704841992418</v>
+        <v>0.3811385650463698</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -539,16 +539,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>12.00939837939213</v>
+        <v>0.8712449723005212</v>
       </c>
       <c r="E4" t="n">
-        <v>9.140591863776882</v>
+        <v>0.05785066144928397</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2168218229579622</v>
+        <v>0.008843279646136596</v>
       </c>
       <c r="G4" t="n">
-        <v>427.3819246160259</v>
+        <v>0.7109464416458999</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -567,16 +567,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>10.55744457957847</v>
+        <v>0.9468755779280924</v>
       </c>
       <c r="E5" t="n">
-        <v>4.448209834596925</v>
+        <v>0.0720382081794736</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07060064480189993</v>
+        <v>0.003657129167761755</v>
       </c>
       <c r="G5" t="n">
-        <v>357.0900572350488</v>
+        <v>0.9581665870669719</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -595,16 +595,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>8.312469899738975</v>
+        <v>0.8045016548549818</v>
       </c>
       <c r="E6" t="n">
-        <v>2.861579430359229</v>
+        <v>0.03821363071046387</v>
       </c>
       <c r="F6" t="n">
-        <v>0.090542040845843</v>
+        <v>0.006228895889722136</v>
       </c>
       <c r="G6" t="n">
-        <v>131.548354232224</v>
+        <v>0.6225969724945055</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -623,16 +623,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>7.914086620417011</v>
+        <v>0.9871415134637862</v>
       </c>
       <c r="E7" t="n">
-        <v>2.317791254550289</v>
+        <v>0.07352686691137612</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1263612323798324</v>
+        <v>0.01359829008596864</v>
       </c>
       <c r="G7" t="n">
-        <v>86.28744571366516</v>
+        <v>0.9992830261476681</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -651,16 +651,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>6.471806066632766</v>
+        <v>0.6453120090476596</v>
       </c>
       <c r="E8" t="n">
-        <v>1.103374230515247</v>
+        <v>0.02181774813526421</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05302902587560862</v>
+        <v>0.004934151793690671</v>
       </c>
       <c r="G8" t="n">
-        <v>54.90554248283681</v>
+        <v>0.4753504397745663</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -677,16 +677,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>68.168040044311</v>
+        <v>5.423980180725023</v>
       </c>
       <c r="E9" t="n">
-        <v>23.57400892583172</v>
+        <v>0.3215650391831476</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09502830464586762</v>
+        <v>0.005557203068385242</v>
       </c>
       <c r="G9" t="n">
-        <v>1295.987932380499</v>
+        <v>4.432079365137422</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>

--- a/01_Thermal/B_results/single_annular_gp_analysis.xlsx
+++ b/01_Thermal/B_results/single_annular_gp_analysis.xlsx
@@ -483,19 +483,19 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5561264840321801</v>
+        <v>0.5343444666976269</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0105389893474099</v>
+        <v>0.007565974587641617</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004869212653042428</v>
+        <v>0.003222045510534377</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2845973329614411</v>
+        <v>0.260528177924342</v>
       </c>
       <c r="H2" t="n">
-        <v>12003.65050354092</v>
+        <v>25095.24045331192</v>
       </c>
     </row>
     <row r="3">
@@ -511,19 +511,19 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6127779690978017</v>
+        <v>0.755838127276955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04757893444987597</v>
+        <v>0.04043025973697661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006235304398978792</v>
+        <v>0.006931189678378079</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3811385650463698</v>
+        <v>0.3313409068848943</v>
       </c>
       <c r="H3" t="n">
-        <v>9803.193489796933</v>
+        <v>6896.988293181215</v>
       </c>
     </row>
     <row r="4">
@@ -539,19 +539,19 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8712449723005212</v>
+        <v>1.103927692003357</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05785066144928397</v>
+        <v>0.1379199422109918</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008843279646136596</v>
+        <v>0.01006828969462627</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7109464416458999</v>
+        <v>1.188232215803369</v>
       </c>
       <c r="H4" t="n">
-        <v>9090.968804657296</v>
+        <v>11721.6815093248</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9468755779280924</v>
+        <v>0.8908477319839812</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0720382081794736</v>
+        <v>0.03572088936062925</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003657129167761755</v>
+        <v>0.003900189459186168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9581665870669719</v>
+        <v>0.6963057632461083</v>
       </c>
       <c r="H5" t="n">
-        <v>71640.79933933762</v>
+        <v>45775.02407050147</v>
       </c>
     </row>
     <row r="6">
@@ -595,19 +595,19 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8045016548549818</v>
+        <v>0.5921066522864671</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03821363071046387</v>
+        <v>0.009761710350692772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.006228895889722136</v>
+        <v>0.004646044913083442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6225969724945055</v>
+        <v>0.3492696160339002</v>
       </c>
       <c r="H6" t="n">
-        <v>16046.66774128612</v>
+        <v>16180.57680150592</v>
       </c>
     </row>
     <row r="7">
@@ -623,19 +623,19 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9871415134637862</v>
+        <v>1.100773482496634</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07352686691137612</v>
+        <v>0.08298556279035579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01359829008596864</v>
+        <v>0.01043674211344744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9992830261476681</v>
+        <v>1.065387561065905</v>
       </c>
       <c r="H7" t="n">
-        <v>5404.056829595331</v>
+        <v>9780.875189666229</v>
       </c>
     </row>
     <row r="8">
@@ -651,19 +651,19 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6453120090476596</v>
+        <v>1.15832965967072</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02181774813526421</v>
+        <v>0.04120683179380095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004934151793690671</v>
+        <v>0.00893957838027405</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4753504397745663</v>
+        <v>0.6805720908328852</v>
       </c>
       <c r="H8" t="n">
-        <v>19524.90314262348</v>
+        <v>8516.086466998437</v>
       </c>
     </row>
     <row r="9">
@@ -677,19 +677,19 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>5.423980180725023</v>
+        <v>6.13616781241574</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3215650391831476</v>
+        <v>0.3555911708310888</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005557203068385242</v>
+        <v>0.006072726408910501</v>
       </c>
       <c r="G9" t="n">
-        <v>4.432079365137422</v>
+        <v>4.571636331791403</v>
       </c>
       <c r="H9" t="n">
-        <v>143514.2398508377</v>
+        <v>123966.47278449</v>
       </c>
     </row>
   </sheetData>
